--- a/AAII_Financials/Quarterly/KYNB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KYNB_QTR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -743,7 +743,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>-16000</v>
+        <v>7500</v>
       </c>
       <c r="E9" s="3">
         <v>1200</v>
@@ -755,7 +755,7 @@
         <v>9400</v>
       </c>
       <c r="H9" s="3">
-        <v>1000</v>
+        <v>22100</v>
       </c>
       <c r="I9" s="3">
         <v>19900</v>
@@ -772,7 +772,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>17200</v>
+        <v>-6300</v>
       </c>
       <c r="E10" s="3">
         <v>-100</v>
@@ -784,7 +784,7 @@
         <v>-6700</v>
       </c>
       <c r="H10" s="3">
-        <v>2100</v>
+        <v>-19000</v>
       </c>
       <c r="I10" s="3">
         <v>-19800</v>
@@ -814,7 +814,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>23500</v>
+        <v>7300</v>
       </c>
       <c r="E12" s="3">
         <v>1200</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="H14" s="3">
-        <v>900</v>
+        <v>-20200</v>
       </c>
       <c r="I14" s="3">
         <v>18600</v>
@@ -952,7 +952,7 @@
         <v>17500</v>
       </c>
       <c r="H17" s="3">
-        <v>9400</v>
+        <v>30500</v>
       </c>
       <c r="I17" s="3">
         <v>29300</v>
@@ -981,7 +981,7 @@
         <v>-14800</v>
       </c>
       <c r="H18" s="3">
-        <v>-6200</v>
+        <v>-27300</v>
       </c>
       <c r="I18" s="3">
         <v>-29100</v>
@@ -1052,7 +1052,7 @@
         <v>-14500</v>
       </c>
       <c r="H21" s="3">
-        <v>-5900</v>
+        <v>-27000</v>
       </c>
       <c r="I21" s="3">
         <v>-28400</v>
@@ -1593,7 +1593,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>4200</v>
       </c>
       <c r="E43" s="3">
         <v>10100</v>
@@ -1650,8 +1650,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>10</v>
+      <c r="D45" s="3">
+        <v>1100</v>
       </c>
       <c r="E45" s="3">
         <v>700</v>
@@ -1749,8 +1749,8 @@
       <c r="G48" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H48" s="3">
-        <v>100</v>
+      <c r="H48" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I48" s="3">
         <v>9700</v>
@@ -1866,7 +1866,7 @@
         <v>16700</v>
       </c>
       <c r="H52" s="3">
-        <v>17900</v>
+        <v>18000</v>
       </c>
       <c r="I52" s="3">
         <v>4400</v>
@@ -2025,7 +2025,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5300</v>
+        <v>16000</v>
       </c>
       <c r="E59" s="3">
         <v>22000</v>
@@ -2095,7 +2095,7 @@
         <v>91200</v>
       </c>
       <c r="H61" s="3">
-        <v>90200</v>
+        <v>90100</v>
       </c>
       <c r="I61" s="3">
         <v>91700</v>
@@ -2124,7 +2124,7 @@
         <v>1000</v>
       </c>
       <c r="H62" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="I62" s="3">
         <v>800</v>
